--- a/services/integrator/internal/document/testdata/stok-nilai-kolom-kode.golden.xlsx
+++ b/services/integrator/internal/document/testdata/stok-nilai-kolom-kode.golden.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">PT Stok Uji</t>
   </si>
@@ -44,6 +44,12 @@
   </si>
   <si>
     <t xml:space="preserve">Gula Aren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Manis</t>
   </si>
   <si>
     <t xml:space="preserve">B001</t>
@@ -285,15 +291,15 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
         <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -353,13 +359,21 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="s">
+      <c r="A20" t="s">
         <v>31</v>
       </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
-        <v>32</v>
+      <c r="B21" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
